--- a/data/processed/harmonization/Major_and_trace_elements_total__Total_potassium/harmonized.xlsx
+++ b/data/processed/harmonization/Major_and_trace_elements_total__Total_potassium/harmonized.xlsx
@@ -432,7 +432,7 @@
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="58" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="49" customWidth="1" min="7" max="7"/>
@@ -518,12 +518,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -614,12 +614,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3:3</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -662,12 +662,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4:4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -710,12 +710,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5:5</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -758,12 +758,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1:6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -806,12 +806,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2:7</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -854,12 +854,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3:8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -902,12 +902,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4:9</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -950,12 +950,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5:10</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -998,12 +998,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6:11</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8:12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>4:20-29</t>
+          <t>Hu:4:20-29</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -4545,7 +4545,7 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4562,12 +4562,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>4:10-20</t>
+          <t>Hu:4:10-20</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4597,7 +4597,7 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4614,12 +4614,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>4:0-10</t>
+          <t>Hu:4:0-10</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4649,7 +4649,7 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4666,12 +4666,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>4:-10-0</t>
+          <t>Ho:4:-10-0</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4701,7 +4701,7 @@
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>4:-20--10</t>
+          <t>Ho:4:-20--10</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4770,12 +4770,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>4:-30--20</t>
+          <t>Ho:4:-30--20</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -4805,7 +4805,7 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>4:-40--30</t>
+          <t>Ho:4:-40--30</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -4857,7 +4857,7 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4874,12 +4874,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>4:-50--40</t>
+          <t>Ho:4:-50--40</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -4909,7 +4909,7 @@
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4926,12 +4926,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>4:-60--50</t>
+          <t>Ho:4:-60--50</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -4961,7 +4961,7 @@
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4978,12 +4978,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>4:-70--60</t>
+          <t>Ho:4:-70--60</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -5013,7 +5013,7 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5030,12 +5030,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>4:-80--70</t>
+          <t>Ho:4:-80--70</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -5065,7 +5065,7 @@
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>4:-90--80</t>
+          <t>Ho:4:-90--80</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -5117,7 +5117,7 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5134,12 +5134,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>4:-100--90</t>
+          <t>Ho:4:-100--90</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -5169,7 +5169,7 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>4:-125--100</t>
+          <t>Ho:4:-125--100</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5238,12 +5238,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>4:-150--125</t>
+          <t>Ho:4:-150--125</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5273,7 +5273,7 @@
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5290,12 +5290,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>4:-175--150</t>
+          <t>Ho:4:-175--150</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5325,7 +5325,7 @@
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5342,12 +5342,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>4:-200--175</t>
+          <t>Ho:4:-200--175</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5377,7 +5377,7 @@
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>4:-250--200</t>
+          <t>Ho:4:-250--200</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -5429,7 +5429,7 @@
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5446,12 +5446,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>5:0-24</t>
+          <t>Hu:5:0-24</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5498,12 +5498,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>5:10-18</t>
+          <t>Hu:5:10-18</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -5533,7 +5533,7 @@
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5550,12 +5550,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>5:0-10</t>
+          <t>Hu:5:0-10</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -5585,7 +5585,7 @@
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5602,12 +5602,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>5:-10-0</t>
+          <t>Ho:5:-10-0</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -5637,7 +5637,7 @@
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5654,12 +5654,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>5:-20--10</t>
+          <t>Ho:5:-20--10</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -5689,7 +5689,7 @@
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5706,12 +5706,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>5:-30--20</t>
+          <t>Ho:5:-30--20</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -5741,7 +5741,7 @@
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5758,12 +5758,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>5:-40--30</t>
+          <t>Ho:5:-40--30</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5810,12 +5810,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>5:-50--40</t>
+          <t>Ho:5:-50--40</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5862,12 +5862,12 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>5:-60--50</t>
+          <t>Ho:5:-60--50</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5914,12 +5914,12 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>5:-70--60</t>
+          <t>Ho:5:-70--60</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -5949,7 +5949,7 @@
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>5:-80--70</t>
+          <t>Ho:5:-80--70</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -6001,7 +6001,7 @@
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6018,12 +6018,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>5:-90--80</t>
+          <t>Ho:5:-90--80</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6070,12 +6070,12 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>5:-100--90</t>
+          <t>Ho:5:-100--90</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -6105,7 +6105,7 @@
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6122,12 +6122,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>5:-125--100</t>
+          <t>Ho:5:-125--100</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -6157,7 +6157,7 @@
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6174,12 +6174,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>5:-150--125</t>
+          <t>Ho:5:-150--125</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       <c r="K116" s="2" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>5:-175--150</t>
+          <t>Ho:5:-175--150</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -6261,7 +6261,7 @@
       <c r="K117" s="2" t="inlineStr"/>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6278,12 +6278,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>5:-200--175</t>
+          <t>Ho:5:-200--175</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -6313,7 +6313,7 @@
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6330,12 +6330,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>5:-250--200</t>
+          <t>Ho:5:-250--200</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       <c r="K119" s="2" t="inlineStr"/>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6382,12 +6382,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>5:-300--250</t>
+          <t>Ho:5:-300--250</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -6417,7 +6417,7 @@
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6434,12 +6434,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>6:20-30</t>
+          <t>Hu:6:20-30</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6486,12 +6486,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>6:10-20</t>
+          <t>Hu:6:10-20</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -6521,7 +6521,7 @@
       <c r="K122" s="2" t="inlineStr"/>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6538,12 +6538,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>6:0-10</t>
+          <t>Hu:6:0-10</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -6573,7 +6573,7 @@
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6590,12 +6590,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>6:10-20</t>
+          <t>Hu:6:10-20</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -6625,7 +6625,7 @@
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6642,12 +6642,12 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>6:0-10</t>
+          <t>Hu:6:0-10</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       <c r="K125" s="2" t="inlineStr"/>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6694,12 +6694,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>6:-10-0</t>
+          <t>Ho:6:-10-0</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6746,12 +6746,12 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>6:-20--10</t>
+          <t>Ho:6:-20--10</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       <c r="K127" s="2" t="inlineStr"/>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6798,12 +6798,12 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>6:-30--20</t>
+          <t>Ho:6:-30--20</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -6833,7 +6833,7 @@
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6850,12 +6850,12 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>6:-40--30</t>
+          <t>Ho:6:-40--30</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -6885,7 +6885,7 @@
       <c r="K129" s="2" t="inlineStr"/>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6902,12 +6902,12 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>6:-50--40</t>
+          <t>Ho:6:-50--40</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -6937,7 +6937,7 @@
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6954,12 +6954,12 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>6:-60--50</t>
+          <t>Ho:6:-60--50</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -6989,7 +6989,7 @@
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7006,12 +7006,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>6:-70--60</t>
+          <t>Ho:6:-70--60</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -7041,7 +7041,7 @@
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7058,12 +7058,12 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>6:-80--70</t>
+          <t>Ho:6:-80--70</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -7093,7 +7093,7 @@
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7110,12 +7110,12 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>6:-90--80</t>
+          <t>Ho:6:-90--80</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7162,12 +7162,12 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>6:-100--90</t>
+          <t>Ho:6:-100--90</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>6:-125--100</t>
+          <t>Ho:6:-125--100</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -7249,7 +7249,7 @@
       <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7266,12 +7266,12 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>6:-150--125</t>
+          <t>Ho:6:-150--125</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7318,12 +7318,12 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>6:-175--150</t>
+          <t>Ho:6:-175--150</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
       <c r="K138" s="2" t="inlineStr"/>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7370,12 +7370,12 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>6:-200--175</t>
+          <t>Ho:6:-200--175</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -7405,7 +7405,7 @@
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7422,12 +7422,12 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>6:-250--200</t>
+          <t>Ho:6:-250--200</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -7457,7 +7457,7 @@
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7474,12 +7474,12 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>7:0-10</t>
+          <t>Hu:7:0-10</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -7509,7 +7509,7 @@
       <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7526,12 +7526,12 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>7:20-22</t>
+          <t>Hu:7:20-22</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -7561,7 +7561,7 @@
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>7:10-20</t>
+          <t>Hu:7:10-20</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -7613,7 +7613,7 @@
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7630,12 +7630,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>7:0-10</t>
+          <t>Hu:7:0-10</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -7665,7 +7665,7 @@
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>7:-10-0</t>
+          <t>Ho:7:-10-0</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -7717,7 +7717,7 @@
       <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7734,12 +7734,12 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>7:-20--10</t>
+          <t>Ho:7:-20--10</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -7769,7 +7769,7 @@
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>7:-30--20</t>
+          <t>Ho:7:-30--20</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -7821,7 +7821,7 @@
       <c r="K147" s="2" t="inlineStr"/>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7838,12 +7838,12 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>7:-40--30</t>
+          <t>Ho:7:-40--30</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -7873,7 +7873,7 @@
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7890,12 +7890,12 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>7:-50--40</t>
+          <t>Ho:7:-50--40</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -7925,7 +7925,7 @@
       <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7942,12 +7942,12 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>7:-60--50</t>
+          <t>Ho:7:-60--50</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7994,12 +7994,12 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>7:-70--60</t>
+          <t>Ho:7:-70--60</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -8029,7 +8029,7 @@
       <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8046,12 +8046,12 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>7:-80--70</t>
+          <t>Ho:7:-80--70</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -8081,7 +8081,7 @@
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8098,12 +8098,12 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>7:-90--80</t>
+          <t>Ho:7:-90--80</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -8133,7 +8133,7 @@
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8150,12 +8150,12 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>7:-100--90</t>
+          <t>Ho:7:-100--90</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -8185,7 +8185,7 @@
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8202,12 +8202,12 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>7:-125--100</t>
+          <t>Ho:7:-125--100</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -8237,7 +8237,7 @@
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>7:-150--125</t>
+          <t>Ho:7:-150--125</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -8289,7 +8289,7 @@
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8306,12 +8306,12 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>7:-175--150</t>
+          <t>Ho:7:-175--150</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -8341,7 +8341,7 @@
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8358,12 +8358,12 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>7:-200--175</t>
+          <t>Ho:7:-200--175</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -8393,7 +8393,7 @@
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8410,12 +8410,12 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>7:-250--200</t>
+          <t>Ho:7:-250--200</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -8445,7 +8445,7 @@
       <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8462,12 +8462,12 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>7:-300--250</t>
+          <t>Ho:7:-300--250</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -8497,7 +8497,7 @@
       <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8514,12 +8514,12 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>8:10-20</t>
+          <t>Hu:8:10-20</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -8549,7 +8549,7 @@
       <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8566,12 +8566,12 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>8:0-10</t>
+          <t>Hu:8:0-10</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -8601,7 +8601,7 @@
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8618,12 +8618,12 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>8:-10-0</t>
+          <t>Hu:8:-10-0</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -8653,7 +8653,7 @@
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8670,12 +8670,12 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>8:-10-0</t>
+          <t>Ho:8:-10-0</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -8705,7 +8705,7 @@
       <c r="K164" s="2" t="inlineStr"/>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8722,12 +8722,12 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>8:-20--10</t>
+          <t>Ho:8:-20--10</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -8757,7 +8757,7 @@
       <c r="K165" s="2" t="inlineStr"/>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8774,12 +8774,12 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>8:-30--20</t>
+          <t>Ho:8:-30--20</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -8809,7 +8809,7 @@
       <c r="K166" s="2" t="inlineStr"/>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8826,12 +8826,12 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>8:-40--30</t>
+          <t>Ho:8:-40--30</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -8861,7 +8861,7 @@
       <c r="K167" s="2" t="inlineStr"/>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8878,12 +8878,12 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>8:-50--40</t>
+          <t>Ho:8:-50--40</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -8913,7 +8913,7 @@
       <c r="K168" s="2" t="inlineStr"/>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8930,12 +8930,12 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>8:-60--50</t>
+          <t>Ho:8:-60--50</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -8965,7 +8965,7 @@
       <c r="K169" s="2" t="inlineStr"/>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8982,12 +8982,12 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>8:-70--60</t>
+          <t>Ho:8:-70--60</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -9017,7 +9017,7 @@
       <c r="K170" s="2" t="inlineStr"/>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9034,12 +9034,12 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>8:-80--70</t>
+          <t>Ho:8:-80--70</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -9069,7 +9069,7 @@
       <c r="K171" s="2" t="inlineStr"/>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9086,12 +9086,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>8:-90--80</t>
+          <t>Ho:8:-90--80</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -9121,7 +9121,7 @@
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9138,12 +9138,12 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>8:-100--90</t>
+          <t>Ho:8:-100--90</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -9173,7 +9173,7 @@
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9190,12 +9190,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>8:-125--100</t>
+          <t>Ho:8:-125--100</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>8:-150--125</t>
+          <t>Ho:8:-150--125</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -9277,7 +9277,7 @@
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>8:-175--150</t>
+          <t>Ho:8:-175--150</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -9329,7 +9329,7 @@
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9346,12 +9346,12 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>8:-200--175</t>
+          <t>Ho:8:-200--175</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -9381,7 +9381,7 @@
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9398,12 +9398,12 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>9:10-18</t>
+          <t>Hu:9:10-18</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -9433,7 +9433,7 @@
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9450,12 +9450,12 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>9:0-10</t>
+          <t>Hu:9:0-10</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -9485,7 +9485,7 @@
       <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>9:-10-0</t>
+          <t>Ho:9:-10-0</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -9537,7 +9537,7 @@
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9554,12 +9554,12 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>9:-20--10</t>
+          <t>Ho:9:-20--10</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>9:-30--20</t>
+          <t>Ho:9:-30--20</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -9641,7 +9641,7 @@
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9658,12 +9658,12 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>9:-40--30</t>
+          <t>Ho:9:-40--30</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -9693,7 +9693,7 @@
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9710,12 +9710,12 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>9:-50--40</t>
+          <t>Ho:9:-50--40</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -9745,7 +9745,7 @@
       <c r="K184" s="2" t="inlineStr"/>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9762,12 +9762,12 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>9:-60--50</t>
+          <t>Ho:9:-60--50</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -9797,7 +9797,7 @@
       <c r="K185" s="2" t="inlineStr"/>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9814,12 +9814,12 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>9:-70--60</t>
+          <t>Ho:9:-70--60</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -9849,7 +9849,7 @@
       <c r="K186" s="2" t="inlineStr"/>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9866,12 +9866,12 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>9:-80--70</t>
+          <t>Ho:9:-80--70</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -9901,7 +9901,7 @@
       <c r="K187" s="2" t="inlineStr"/>
       <c r="L187" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9918,12 +9918,12 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>9:-100--90</t>
+          <t>Ho:9:-100--90</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -9953,7 +9953,7 @@
       <c r="K188" s="2" t="inlineStr"/>
       <c r="L188" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9970,12 +9970,12 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>9:-125--100</t>
+          <t>Ho:9:-125--100</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -10005,7 +10005,7 @@
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>9:-150--125</t>
+          <t>Ho:9:-150--125</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -10057,7 +10057,7 @@
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>9:-175--150</t>
+          <t>Ho:9:-175--150</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -10109,7 +10109,7 @@
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>9:-200--175</t>
+          <t>Ho:9:-200--175</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -10161,7 +10161,7 @@
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10178,12 +10178,12 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>9:-250--200</t>
+          <t>Ho:9:-250--200</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10230,12 +10230,12 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>9:-300--250</t>
+          <t>Ho:9:-300--250</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -10265,7 +10265,7 @@
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10282,12 +10282,12 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>10:20-29</t>
+          <t>Hu:10:20-29</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -10317,7 +10317,7 @@
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10334,12 +10334,12 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>10:10-20</t>
+          <t>Hu:10:10-20</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -10369,7 +10369,7 @@
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10386,12 +10386,12 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>10:0-10</t>
+          <t>Hu:10:0-10</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -10421,7 +10421,7 @@
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>10:-10-0</t>
+          <t>Ho:10:-10-0</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -10473,7 +10473,7 @@
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10490,12 +10490,12 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>10:-20--10</t>
+          <t>Ho:10:-20--10</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -10525,7 +10525,7 @@
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10542,12 +10542,12 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>10:-30--20</t>
+          <t>Ho:10:-30--20</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -10577,7 +10577,7 @@
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10594,12 +10594,12 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>10:-40--30</t>
+          <t>Ho:10:-40--30</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -10629,7 +10629,7 @@
       <c r="K201" s="2" t="inlineStr"/>
       <c r="L201" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>10:-50--40</t>
+          <t>Ho:10:-50--40</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -10681,7 +10681,7 @@
       <c r="K202" s="2" t="inlineStr"/>
       <c r="L202" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10698,12 +10698,12 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>10:-60--50</t>
+          <t>Ho:10:-60--50</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -10733,7 +10733,7 @@
       <c r="K203" s="2" t="inlineStr"/>
       <c r="L203" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10750,12 +10750,12 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>10:-70--60</t>
+          <t>Ho:10:-70--60</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -10785,7 +10785,7 @@
       <c r="K204" s="2" t="inlineStr"/>
       <c r="L204" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10802,12 +10802,12 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>10:-80--70</t>
+          <t>Ho:10:-80--70</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -10837,7 +10837,7 @@
       <c r="K205" s="2" t="inlineStr"/>
       <c r="L205" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10854,12 +10854,12 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>10:-90--80</t>
+          <t>Ho:10:-90--80</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -10889,7 +10889,7 @@
       <c r="K206" s="2" t="inlineStr"/>
       <c r="L206" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10906,12 +10906,12 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>10:-100--90</t>
+          <t>Ho:10:-100--90</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -10941,7 +10941,7 @@
       <c r="K207" s="2" t="inlineStr"/>
       <c r="L207" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10958,12 +10958,12 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>10:-125--100</t>
+          <t>Ho:10:-125--100</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -10993,7 +10993,7 @@
       <c r="K208" s="2" t="inlineStr"/>
       <c r="L208" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11010,12 +11010,12 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>10:-150--125</t>
+          <t>Ho:10:-150--125</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -11045,7 +11045,7 @@
       <c r="K209" s="2" t="inlineStr"/>
       <c r="L209" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11062,12 +11062,12 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>10:-175--150</t>
+          <t>Ho:10:-175--150</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -11097,7 +11097,7 @@
       <c r="K210" s="2" t="inlineStr"/>
       <c r="L210" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11114,12 +11114,12 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>10:-200--175</t>
+          <t>Ho:10:-200--175</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -11149,7 +11149,7 @@
       <c r="K211" s="2" t="inlineStr"/>
       <c r="L211" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11166,12 +11166,12 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>10:-225--200</t>
+          <t>Ho:10:-225--200</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -11201,7 +11201,7 @@
       <c r="K212" s="2" t="inlineStr"/>
       <c r="L212" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11218,12 +11218,12 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>10:-255--225</t>
+          <t>Ho:10:-255--225</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
@@ -11253,7 +11253,7 @@
       <c r="K213" s="2" t="inlineStr"/>
       <c r="L213" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11270,12 +11270,12 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>10:-275--255</t>
+          <t>Ho:10:-275--255</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -11305,7 +11305,7 @@
       <c r="K214" s="2" t="inlineStr"/>
       <c r="L214" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11322,12 +11322,12 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>11:10-18</t>
+          <t>Hu:11:10-18</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -11357,7 +11357,7 @@
       <c r="K215" s="2" t="inlineStr"/>
       <c r="L215" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11374,12 +11374,12 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>11:0-10</t>
+          <t>Hu:11:0-10</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -11409,7 +11409,7 @@
       <c r="K216" s="2" t="inlineStr"/>
       <c r="L216" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>11:-10-0</t>
+          <t>Ho:11:-10-0</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -11461,7 +11461,7 @@
       <c r="K217" s="2" t="inlineStr"/>
       <c r="L217" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11478,12 +11478,12 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>11:-20--10</t>
+          <t>Ho:11:-20--10</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -11513,7 +11513,7 @@
       <c r="K218" s="2" t="inlineStr"/>
       <c r="L218" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11530,12 +11530,12 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>11:-30--20</t>
+          <t>Ho:11:-30--20</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -11565,7 +11565,7 @@
       <c r="K219" s="2" t="inlineStr"/>
       <c r="L219" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11582,12 +11582,12 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>11:-40--30</t>
+          <t>Ho:11:-40--30</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -11617,7 +11617,7 @@
       <c r="K220" s="2" t="inlineStr"/>
       <c r="L220" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11634,12 +11634,12 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>11:-50--40</t>
+          <t>Ho:11:-50--40</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -11669,7 +11669,7 @@
       <c r="K221" s="2" t="inlineStr"/>
       <c r="L221" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11686,12 +11686,12 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>11:-60--50</t>
+          <t>Ho:11:-60--50</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -11721,7 +11721,7 @@
       <c r="K222" s="2" t="inlineStr"/>
       <c r="L222" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11738,12 +11738,12 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>11:-70--60</t>
+          <t>Ho:11:-70--60</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -11773,7 +11773,7 @@
       <c r="K223" s="2" t="inlineStr"/>
       <c r="L223" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11790,12 +11790,12 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>11:-80--70</t>
+          <t>Ho:11:-80--70</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -11825,7 +11825,7 @@
       <c r="K224" s="2" t="inlineStr"/>
       <c r="L224" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11842,12 +11842,12 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>11:-90--80</t>
+          <t>Ho:11:-90--80</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -11877,7 +11877,7 @@
       <c r="K225" s="2" t="inlineStr"/>
       <c r="L225" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11894,12 +11894,12 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>11:-100--90</t>
+          <t>Ho:11:-100--90</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -11929,7 +11929,7 @@
       <c r="K226" s="2" t="inlineStr"/>
       <c r="L226" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11946,12 +11946,12 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>11:-125--100</t>
+          <t>Ho:11:-125--100</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -11981,7 +11981,7 @@
       <c r="K227" s="2" t="inlineStr"/>
       <c r="L227" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>11:-150--125</t>
+          <t>Ho:11:-150--125</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -12033,7 +12033,7 @@
       <c r="K228" s="2" t="inlineStr"/>
       <c r="L228" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12050,12 +12050,12 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>11:-175--150</t>
+          <t>Ho:11:-175--150</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -12085,7 +12085,7 @@
       <c r="K229" s="2" t="inlineStr"/>
       <c r="L229" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12102,12 +12102,12 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>11:-200--175</t>
+          <t>Ho:11:-200--175</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -12137,7 +12137,7 @@
       <c r="K230" s="2" t="inlineStr"/>
       <c r="L230" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12154,12 +12154,12 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>11:-250--200</t>
+          <t>Ho:11:-250--200</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -12189,7 +12189,7 @@
       <c r="K231" s="2" t="inlineStr"/>
       <c r="L231" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12206,12 +12206,12 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>13:20-25</t>
+          <t>Hu:13:20-25</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -12241,7 +12241,7 @@
       <c r="K232" s="2" t="inlineStr"/>
       <c r="L232" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12258,12 +12258,12 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>13:10-20</t>
+          <t>Hu:13:10-20</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -12293,7 +12293,7 @@
       <c r="K233" s="2" t="inlineStr"/>
       <c r="L233" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12310,12 +12310,12 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>13:0-10</t>
+          <t>Hu:13:0-10</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -12345,7 +12345,7 @@
       <c r="K234" s="2" t="inlineStr"/>
       <c r="L234" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12362,12 +12362,12 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>13:-10-0</t>
+          <t>Hu:13:-10-0</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -12397,7 +12397,7 @@
       <c r="K235" s="2" t="inlineStr"/>
       <c r="L235" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12414,12 +12414,12 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>13:-10-0</t>
+          <t>Ho:13:-10-0</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -12449,7 +12449,7 @@
       <c r="K236" s="2" t="inlineStr"/>
       <c r="L236" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>13:-20--10</t>
+          <t>Ho:13:-20--10</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -12501,7 +12501,7 @@
       <c r="K237" s="2" t="inlineStr"/>
       <c r="L237" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12518,12 +12518,12 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>13:-30--20</t>
+          <t>Ho:13:-30--20</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -12553,7 +12553,7 @@
       <c r="K238" s="2" t="inlineStr"/>
       <c r="L238" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12570,12 +12570,12 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>13:-40--30</t>
+          <t>Ho:13:-40--30</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -12605,7 +12605,7 @@
       <c r="K239" s="2" t="inlineStr"/>
       <c r="L239" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12622,12 +12622,12 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>13:-50--40</t>
+          <t>Ho:13:-50--40</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -12657,7 +12657,7 @@
       <c r="K240" s="2" t="inlineStr"/>
       <c r="L240" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12674,12 +12674,12 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>13:-60--50</t>
+          <t>Ho:13:-60--50</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -12709,7 +12709,7 @@
       <c r="K241" s="2" t="inlineStr"/>
       <c r="L241" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12726,12 +12726,12 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>13:-70--60</t>
+          <t>Ho:13:-70--60</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -12761,7 +12761,7 @@
       <c r="K242" s="2" t="inlineStr"/>
       <c r="L242" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12778,12 +12778,12 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>13:-80--70</t>
+          <t>Ho:13:-80--70</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -12813,7 +12813,7 @@
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12830,12 +12830,12 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>13:-90--80</t>
+          <t>Ho:13:-90--80</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
@@ -12865,7 +12865,7 @@
       <c r="K244" s="2" t="inlineStr"/>
       <c r="L244" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12882,12 +12882,12 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>13:-100--90</t>
+          <t>Ho:13:-100--90</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
@@ -12917,7 +12917,7 @@
       <c r="K245" s="2" t="inlineStr"/>
       <c r="L245" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12934,12 +12934,12 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>13:-125--100</t>
+          <t>Ho:13:-125--100</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -12969,7 +12969,7 @@
       <c r="K246" s="2" t="inlineStr"/>
       <c r="L246" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12986,12 +12986,12 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>13:-150--125</t>
+          <t>Ho:13:-150--125</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -13021,7 +13021,7 @@
       <c r="K247" s="2" t="inlineStr"/>
       <c r="L247" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13038,12 +13038,12 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>13:-175--150</t>
+          <t>Ho:13:-175--150</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
@@ -13073,7 +13073,7 @@
       <c r="K248" s="2" t="inlineStr"/>
       <c r="L248" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13090,12 +13090,12 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>13:-200--175</t>
+          <t>Ho:13:-200--175</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
@@ -13125,7 +13125,7 @@
       <c r="K249" s="2" t="inlineStr"/>
       <c r="L249" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13142,12 +13142,12 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>13:-250--200</t>
+          <t>Ho:13:-250--200</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -13177,7 +13177,7 @@
       <c r="K250" s="2" t="inlineStr"/>
       <c r="L250" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13194,12 +13194,12 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>13:-270--250</t>
+          <t>Ho:13:-270--250</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
@@ -13229,7 +13229,7 @@
       <c r="K251" s="2" t="inlineStr"/>
       <c r="L251" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>13:-300--270</t>
+          <t>Ho:13:-300--270</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -13281,7 +13281,7 @@
       <c r="K252" s="2" t="inlineStr"/>
       <c r="L252" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13298,12 +13298,12 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>14:0-10</t>
+          <t>Hu:14:0-10</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -13333,7 +13333,7 @@
       <c r="K253" s="2" t="inlineStr"/>
       <c r="L253" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13350,12 +13350,12 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>14:-10-0</t>
+          <t>Ho:14:-10-0</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
@@ -13385,7 +13385,7 @@
       <c r="K254" s="2" t="inlineStr"/>
       <c r="L254" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13402,12 +13402,12 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>14:-20--10</t>
+          <t>Ho:14:-20--10</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
@@ -13437,7 +13437,7 @@
       <c r="K255" s="2" t="inlineStr"/>
       <c r="L255" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13454,12 +13454,12 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>14:-30--20</t>
+          <t>Ho:14:-30--20</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
@@ -13489,7 +13489,7 @@
       <c r="K256" s="2" t="inlineStr"/>
       <c r="L256" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13506,12 +13506,12 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>14:-40--30</t>
+          <t>Ho:14:-40--30</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
@@ -13541,7 +13541,7 @@
       <c r="K257" s="2" t="inlineStr"/>
       <c r="L257" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13558,12 +13558,12 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>14:-50--40</t>
+          <t>Ho:14:-50--40</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
@@ -13593,7 +13593,7 @@
       <c r="K258" s="2" t="inlineStr"/>
       <c r="L258" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>14:-60--50</t>
+          <t>Ho:14:-60--50</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
@@ -13645,7 +13645,7 @@
       <c r="K259" s="2" t="inlineStr"/>
       <c r="L259" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13662,12 +13662,12 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>14:-70--60</t>
+          <t>Ho:14:-70--60</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -13697,7 +13697,7 @@
       <c r="K260" s="2" t="inlineStr"/>
       <c r="L260" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13714,12 +13714,12 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>14:-80--70</t>
+          <t>Ho:14:-80--70</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
@@ -13749,7 +13749,7 @@
       <c r="K261" s="2" t="inlineStr"/>
       <c r="L261" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13766,12 +13766,12 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>14:-90--80</t>
+          <t>Ho:14:-90--80</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -13801,7 +13801,7 @@
       <c r="K262" s="2" t="inlineStr"/>
       <c r="L262" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>14:-100--90</t>
+          <t>Ho:14:-100--90</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
@@ -13853,7 +13853,7 @@
       <c r="K263" s="2" t="inlineStr"/>
       <c r="L263" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13870,12 +13870,12 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>14:-125--100</t>
+          <t>Ho:14:-125--100</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
@@ -13905,7 +13905,7 @@
       <c r="K264" s="2" t="inlineStr"/>
       <c r="L264" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13922,12 +13922,12 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>14:-150--125</t>
+          <t>Ho:14:-150--125</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
@@ -13957,7 +13957,7 @@
       <c r="K265" s="2" t="inlineStr"/>
       <c r="L265" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13974,12 +13974,12 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>14:-175--150</t>
+          <t>Ho:14:-175--150</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
@@ -14009,7 +14009,7 @@
       <c r="K266" s="2" t="inlineStr"/>
       <c r="L266" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14026,12 +14026,12 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>14:-200--175</t>
+          <t>Ho:14:-200--175</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
@@ -14061,7 +14061,7 @@
       <c r="K267" s="2" t="inlineStr"/>
       <c r="L267" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14078,12 +14078,12 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>14:-215--200</t>
+          <t>Ho:14:-215--200</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -14113,7 +14113,7 @@
       <c r="K268" s="2" t="inlineStr"/>
       <c r="L268" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14130,12 +14130,12 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>14:-220--215</t>
+          <t>Ho:14:-220--215</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
@@ -14165,7 +14165,7 @@
       <c r="K269" s="2" t="inlineStr"/>
       <c r="L269" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14182,12 +14182,12 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>15:20-24</t>
+          <t>Hu:15:20-24</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
@@ -14217,7 +14217,7 @@
       <c r="K270" s="2" t="inlineStr"/>
       <c r="L270" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14234,12 +14234,12 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>15:10-20</t>
+          <t>Hu:15:10-20</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
@@ -14269,7 +14269,7 @@
       <c r="K271" s="2" t="inlineStr"/>
       <c r="L271" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14286,12 +14286,12 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>15:0-10</t>
+          <t>Hu:15:0-10</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
@@ -14321,7 +14321,7 @@
       <c r="K272" s="2" t="inlineStr"/>
       <c r="L272" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14338,12 +14338,12 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>15:-10-0</t>
+          <t>Hu:15:-10-0</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
@@ -14373,7 +14373,7 @@
       <c r="K273" s="2" t="inlineStr"/>
       <c r="L273" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14390,12 +14390,12 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>15:-10-0</t>
+          <t>Ho:15:-10-0</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
@@ -14425,7 +14425,7 @@
       <c r="K274" s="2" t="inlineStr"/>
       <c r="L274" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14442,12 +14442,12 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>15:-20--10</t>
+          <t>Ho:15:-20--10</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
@@ -14477,7 +14477,7 @@
       <c r="K275" s="2" t="inlineStr"/>
       <c r="L275" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14494,12 +14494,12 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>15:-30--20</t>
+          <t>Ho:15:-30--20</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
@@ -14529,7 +14529,7 @@
       <c r="K276" s="2" t="inlineStr"/>
       <c r="L276" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14546,12 +14546,12 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>15:-40--30</t>
+          <t>Ho:15:-40--30</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
@@ -14581,7 +14581,7 @@
       <c r="K277" s="2" t="inlineStr"/>
       <c r="L277" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14598,12 +14598,12 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>15:-60--50</t>
+          <t>Ho:15:-60--50</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
@@ -14633,7 +14633,7 @@
       <c r="K278" s="2" t="inlineStr"/>
       <c r="L278" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14650,12 +14650,12 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>15:-70--60</t>
+          <t>Ho:15:-70--60</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
@@ -14685,7 +14685,7 @@
       <c r="K279" s="2" t="inlineStr"/>
       <c r="L279" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14702,12 +14702,12 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>15:-80--70</t>
+          <t>Ho:15:-80--70</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -14737,7 +14737,7 @@
       <c r="K280" s="2" t="inlineStr"/>
       <c r="L280" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14754,12 +14754,12 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>15:-90--80</t>
+          <t>Ho:15:-90--80</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
@@ -14789,7 +14789,7 @@
       <c r="K281" s="2" t="inlineStr"/>
       <c r="L281" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14806,12 +14806,12 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>15:-100--90</t>
+          <t>Ho:15:-100--90</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -14841,7 +14841,7 @@
       <c r="K282" s="2" t="inlineStr"/>
       <c r="L282" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14858,12 +14858,12 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>15:-125--100</t>
+          <t>Ho:15:-125--100</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
@@ -14893,7 +14893,7 @@
       <c r="K283" s="2" t="inlineStr"/>
       <c r="L283" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14910,12 +14910,12 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>15:-150--125</t>
+          <t>Ho:15:-150--125</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
@@ -14945,7 +14945,7 @@
       <c r="K284" s="2" t="inlineStr"/>
       <c r="L284" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14962,12 +14962,12 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>16:20-29</t>
+          <t>Hu:16:20-29</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
@@ -14997,7 +14997,7 @@
       <c r="K285" s="2" t="inlineStr"/>
       <c r="L285" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15014,12 +15014,12 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>16:10-20</t>
+          <t>Hu:16:10-20</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
@@ -15049,7 +15049,7 @@
       <c r="K286" s="2" t="inlineStr"/>
       <c r="L286" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>16:0-10</t>
+          <t>Hu:16:0-10</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
@@ -15101,7 +15101,7 @@
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15118,12 +15118,12 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>16:-10-0</t>
+          <t>Hu:16:-10-0</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
@@ -15153,7 +15153,7 @@
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15170,12 +15170,12 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>16:-10-0</t>
+          <t>Ho:16:-10-0</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
@@ -15205,7 +15205,7 @@
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15222,12 +15222,12 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>16:-20--10</t>
+          <t>Ho:16:-20--10</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
@@ -15257,7 +15257,7 @@
       <c r="K290" s="2" t="inlineStr"/>
       <c r="L290" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15274,12 +15274,12 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>16:-30--20</t>
+          <t>Ho:16:-30--20</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
@@ -15309,7 +15309,7 @@
       <c r="K291" s="2" t="inlineStr"/>
       <c r="L291" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15326,12 +15326,12 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>16:-40--30</t>
+          <t>Ho:16:-40--30</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
@@ -15361,7 +15361,7 @@
       <c r="K292" s="2" t="inlineStr"/>
       <c r="L292" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15378,12 +15378,12 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>16:-50--40</t>
+          <t>Ho:16:-50--40</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
@@ -15413,7 +15413,7 @@
       <c r="K293" s="2" t="inlineStr"/>
       <c r="L293" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15430,12 +15430,12 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>16:-60--50</t>
+          <t>Ho:16:-60--50</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
@@ -15465,7 +15465,7 @@
       <c r="K294" s="2" t="inlineStr"/>
       <c r="L294" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15482,12 +15482,12 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>16:-70--60</t>
+          <t>Ho:16:-70--60</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
@@ -15517,7 +15517,7 @@
       <c r="K295" s="2" t="inlineStr"/>
       <c r="L295" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15534,12 +15534,12 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>16:-80--70</t>
+          <t>Ho:16:-80--70</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
@@ -15569,7 +15569,7 @@
       <c r="K296" s="2" t="inlineStr"/>
       <c r="L296" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15586,12 +15586,12 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>16:-90--80</t>
+          <t>Ho:16:-90--80</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
@@ -15621,7 +15621,7 @@
       <c r="K297" s="2" t="inlineStr"/>
       <c r="L297" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15638,12 +15638,12 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>16:-100--90</t>
+          <t>Ho:16:-100--90</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
@@ -15673,7 +15673,7 @@
       <c r="K298" s="2" t="inlineStr"/>
       <c r="L298" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15690,12 +15690,12 @@
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>16:-125--100</t>
+          <t>Ho:16:-125--100</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
@@ -15725,7 +15725,7 @@
       <c r="K299" s="2" t="inlineStr"/>
       <c r="L299" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15742,12 +15742,12 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>16:-150--125</t>
+          <t>Ho:16:-150--125</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
@@ -15777,7 +15777,7 @@
       <c r="K300" s="2" t="inlineStr"/>
       <c r="L300" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15794,12 +15794,12 @@
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>16:-175--150</t>
+          <t>Ho:16:-175--150</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
@@ -15829,7 +15829,7 @@
       <c r="K301" s="2" t="inlineStr"/>
       <c r="L301" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15846,12 +15846,12 @@
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>16:-200--175</t>
+          <t>Ho:16:-200--175</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
@@ -15881,7 +15881,7 @@
       <c r="K302" s="2" t="inlineStr"/>
       <c r="L302" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15898,12 +15898,12 @@
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>16:-250--200</t>
+          <t>Ho:16:-250--200</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
@@ -15933,7 +15933,7 @@
       <c r="K303" s="2" t="inlineStr"/>
       <c r="L303" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15950,12 +15950,12 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>17:20-25</t>
+          <t>Hu:17:20-25</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
@@ -15985,7 +15985,7 @@
       <c r="K304" s="2" t="inlineStr"/>
       <c r="L304" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16002,12 +16002,12 @@
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>17:10-20</t>
+          <t>Hu:17:10-20</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
@@ -16037,7 +16037,7 @@
       <c r="K305" s="2" t="inlineStr"/>
       <c r="L305" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16054,12 +16054,12 @@
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>17:0-10</t>
+          <t>Hu:17:0-10</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
@@ -16089,7 +16089,7 @@
       <c r="K306" s="2" t="inlineStr"/>
       <c r="L306" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16106,12 +16106,12 @@
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>17:-10-0</t>
+          <t>Hu:17:-10-0</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
@@ -16141,7 +16141,7 @@
       <c r="K307" s="2" t="inlineStr"/>
       <c r="L307" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16158,12 +16158,12 @@
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>17:-10-0</t>
+          <t>Ho:17:-10-0</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
@@ -16193,7 +16193,7 @@
       <c r="K308" s="2" t="inlineStr"/>
       <c r="L308" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16210,12 +16210,12 @@
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>17:-20--10</t>
+          <t>Ho:17:-20--10</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
@@ -16245,7 +16245,7 @@
       <c r="K309" s="2" t="inlineStr"/>
       <c r="L309" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16262,12 +16262,12 @@
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>17:-30--20</t>
+          <t>Ho:17:-30--20</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
@@ -16297,7 +16297,7 @@
       <c r="K310" s="2" t="inlineStr"/>
       <c r="L310" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16314,12 +16314,12 @@
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>17:-40--30</t>
+          <t>Ho:17:-40--30</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
@@ -16349,7 +16349,7 @@
       <c r="K311" s="2" t="inlineStr"/>
       <c r="L311" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16366,12 +16366,12 @@
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>17:-50--40</t>
+          <t>Ho:17:-50--40</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
@@ -16401,7 +16401,7 @@
       <c r="K312" s="2" t="inlineStr"/>
       <c r="L312" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16418,12 +16418,12 @@
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>17:-60--50</t>
+          <t>Ho:17:-60--50</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
@@ -16453,7 +16453,7 @@
       <c r="K313" s="2" t="inlineStr"/>
       <c r="L313" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16470,12 +16470,12 @@
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>17:-70--60</t>
+          <t>Ho:17:-70--60</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
@@ -16505,7 +16505,7 @@
       <c r="K314" s="2" t="inlineStr"/>
       <c r="L314" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16522,12 +16522,12 @@
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>17:-80--70</t>
+          <t>Ho:17:-80--70</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
@@ -16557,7 +16557,7 @@
       <c r="K315" s="2" t="inlineStr"/>
       <c r="L315" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16574,12 +16574,12 @@
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>17:-90--80</t>
+          <t>Ho:17:-90--80</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
@@ -16609,7 +16609,7 @@
       <c r="K316" s="2" t="inlineStr"/>
       <c r="L316" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16626,12 +16626,12 @@
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>17:-100--90</t>
+          <t>Ho:17:-100--90</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
@@ -16661,7 +16661,7 @@
       <c r="K317" s="2" t="inlineStr"/>
       <c r="L317" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16678,12 +16678,12 @@
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>17:-125--100</t>
+          <t>Ho:17:-125--100</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
@@ -16713,7 +16713,7 @@
       <c r="K318" s="2" t="inlineStr"/>
       <c r="L318" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16730,12 +16730,12 @@
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>17:-150--125</t>
+          <t>Ho:17:-150--125</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
@@ -16765,7 +16765,7 @@
       <c r="K319" s="2" t="inlineStr"/>
       <c r="L319" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16782,12 +16782,12 @@
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>17:-175--150</t>
+          <t>Ho:17:-175--150</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
@@ -16817,7 +16817,7 @@
       <c r="K320" s="2" t="inlineStr"/>
       <c r="L320" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16834,12 +16834,12 @@
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>17:-200--175</t>
+          <t>Ho:17:-200--175</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
@@ -16869,7 +16869,7 @@
       <c r="K321" s="2" t="inlineStr"/>
       <c r="L321" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16886,12 +16886,12 @@
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>17:-239--200</t>
+          <t>Ho:17:-239--200</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
@@ -16921,7 +16921,7 @@
       <c r="K322" s="2" t="inlineStr"/>
       <c r="L322" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16938,12 +16938,12 @@
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>19:10-20</t>
+          <t>Hu:19:10-20</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
@@ -16973,7 +16973,7 @@
       <c r="K323" s="2" t="inlineStr"/>
       <c r="L323" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16990,12 +16990,12 @@
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>19:0-10</t>
+          <t>Hu:19:0-10</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
@@ -17025,7 +17025,7 @@
       <c r="K324" s="2" t="inlineStr"/>
       <c r="L324" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17042,12 +17042,12 @@
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>19:-10-0</t>
+          <t>Ho:19:-10-0</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
@@ -17077,7 +17077,7 @@
       <c r="K325" s="2" t="inlineStr"/>
       <c r="L325" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17094,12 +17094,12 @@
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>19:-20--10</t>
+          <t>Ho:19:-20--10</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
@@ -17129,7 +17129,7 @@
       <c r="K326" s="2" t="inlineStr"/>
       <c r="L326" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17146,12 +17146,12 @@
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>19:-30--20</t>
+          <t>Ho:19:-30--20</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
@@ -17181,7 +17181,7 @@
       <c r="K327" s="2" t="inlineStr"/>
       <c r="L327" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17198,12 +17198,12 @@
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>19:-40--30</t>
+          <t>Ho:19:-40--30</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
@@ -17233,7 +17233,7 @@
       <c r="K328" s="2" t="inlineStr"/>
       <c r="L328" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17250,12 +17250,12 @@
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>19:-50--40</t>
+          <t>Ho:19:-50--40</t>
         </is>
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
@@ -17285,7 +17285,7 @@
       <c r="K329" s="2" t="inlineStr"/>
       <c r="L329" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17302,12 +17302,12 @@
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>19:-60--50</t>
+          <t>Ho:19:-60--50</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
@@ -17337,7 +17337,7 @@
       <c r="K330" s="2" t="inlineStr"/>
       <c r="L330" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17354,12 +17354,12 @@
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>19:-70--60</t>
+          <t>Ho:19:-70--60</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
@@ -17389,7 +17389,7 @@
       <c r="K331" s="2" t="inlineStr"/>
       <c r="L331" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17406,12 +17406,12 @@
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>19:-80--70</t>
+          <t>Ho:19:-80--70</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
@@ -17441,7 +17441,7 @@
       <c r="K332" s="2" t="inlineStr"/>
       <c r="L332" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17458,12 +17458,12 @@
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>19:-90--80</t>
+          <t>Ho:19:-90--80</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
@@ -17493,7 +17493,7 @@
       <c r="K333" s="2" t="inlineStr"/>
       <c r="L333" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17510,12 +17510,12 @@
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>19:-100--90</t>
+          <t>Ho:19:-100--90</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
@@ -17545,7 +17545,7 @@
       <c r="K334" s="2" t="inlineStr"/>
       <c r="L334" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17562,12 +17562,12 @@
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>19:-125--100</t>
+          <t>Ho:19:-125--100</t>
         </is>
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
@@ -17597,7 +17597,7 @@
       <c r="K335" s="2" t="inlineStr"/>
       <c r="L335" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17614,12 +17614,12 @@
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>19:-150--125</t>
+          <t>Ho:19:-150--125</t>
         </is>
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
@@ -17649,7 +17649,7 @@
       <c r="K336" s="2" t="inlineStr"/>
       <c r="L336" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17666,12 +17666,12 @@
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>19:-175--150</t>
+          <t>Ho:19:-175--150</t>
         </is>
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
@@ -17701,7 +17701,7 @@
       <c r="K337" s="2" t="inlineStr"/>
       <c r="L337" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>19:-200--175</t>
+          <t>Ho:19:-200--175</t>
         </is>
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
@@ -17753,7 +17753,7 @@
       <c r="K338" s="2" t="inlineStr"/>
       <c r="L338" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17770,12 +17770,12 @@
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>19:-216--200</t>
+          <t>Ho:19:-216--200</t>
         </is>
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr">
@@ -17805,7 +17805,7 @@
       <c r="K339" s="2" t="inlineStr"/>
       <c r="L339" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17822,12 +17822,12 @@
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>19:-250--216</t>
+          <t>Ho:19:-250--216</t>
         </is>
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
@@ -17857,7 +17857,7 @@
       <c r="K340" s="2" t="inlineStr"/>
       <c r="L340" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17874,12 +17874,12 @@
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>20:10-19</t>
+          <t>Hu:20:10-19</t>
         </is>
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr">
@@ -17909,7 +17909,7 @@
       <c r="K341" s="2" t="inlineStr"/>
       <c r="L341" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17926,12 +17926,12 @@
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>20:0-10</t>
+          <t>Hu:20:0-10</t>
         </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
@@ -17961,7 +17961,7 @@
       <c r="K342" s="2" t="inlineStr"/>
       <c r="L342" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17978,12 +17978,12 @@
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>20:-10-0</t>
+          <t>Hu:20:-10-0</t>
         </is>
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr">
@@ -18013,7 +18013,7 @@
       <c r="K343" s="2" t="inlineStr"/>
       <c r="L343" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18030,12 +18030,12 @@
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>20:-10-0</t>
+          <t>Ho:20:-10-0</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
@@ -18065,7 +18065,7 @@
       <c r="K344" s="2" t="inlineStr"/>
       <c r="L344" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18082,12 +18082,12 @@
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>20:-20--10</t>
+          <t>Ho:20:-20--10</t>
         </is>
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
@@ -18117,7 +18117,7 @@
       <c r="K345" s="2" t="inlineStr"/>
       <c r="L345" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18134,12 +18134,12 @@
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>20:-30--20</t>
+          <t>Ho:20:-30--20</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
@@ -18169,7 +18169,7 @@
       <c r="K346" s="2" t="inlineStr"/>
       <c r="L346" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18186,12 +18186,12 @@
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>20:-40--30</t>
+          <t>Ho:20:-40--30</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
@@ -18221,7 +18221,7 @@
       <c r="K347" s="2" t="inlineStr"/>
       <c r="L347" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18238,12 +18238,12 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>20:-50--40</t>
+          <t>Ho:20:-50--40</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
@@ -18273,7 +18273,7 @@
       <c r="K348" s="2" t="inlineStr"/>
       <c r="L348" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18290,12 +18290,12 @@
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>20:-60--50</t>
+          <t>Ho:20:-60--50</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
@@ -18325,7 +18325,7 @@
       <c r="K349" s="2" t="inlineStr"/>
       <c r="L349" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18342,12 +18342,12 @@
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>20:-70--60</t>
+          <t>Ho:20:-70--60</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
@@ -18377,7 +18377,7 @@
       <c r="K350" s="2" t="inlineStr"/>
       <c r="L350" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18394,12 +18394,12 @@
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>20:-80--70</t>
+          <t>Ho:20:-80--70</t>
         </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr">
@@ -18429,7 +18429,7 @@
       <c r="K351" s="2" t="inlineStr"/>
       <c r="L351" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18446,12 +18446,12 @@
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>20:-90--80</t>
+          <t>Ho:20:-90--80</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
@@ -18481,7 +18481,7 @@
       <c r="K352" s="2" t="inlineStr"/>
       <c r="L352" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18498,12 +18498,12 @@
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>20:-100--90</t>
+          <t>Ho:20:-100--90</t>
         </is>
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
@@ -18533,7 +18533,7 @@
       <c r="K353" s="2" t="inlineStr"/>
       <c r="L353" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18550,12 +18550,12 @@
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>20:-125--100</t>
+          <t>Ho:20:-125--100</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
@@ -18585,7 +18585,7 @@
       <c r="K354" s="2" t="inlineStr"/>
       <c r="L354" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18602,12 +18602,12 @@
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>20:-150--125</t>
+          <t>Ho:20:-150--125</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
@@ -18637,7 +18637,7 @@
       <c r="K355" s="2" t="inlineStr"/>
       <c r="L355" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18654,12 +18654,12 @@
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>20:-175--150</t>
+          <t>Ho:20:-175--150</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
@@ -18689,7 +18689,7 @@
       <c r="K356" s="2" t="inlineStr"/>
       <c r="L356" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18706,12 +18706,12 @@
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>20:-200--175</t>
+          <t>Ho:20:-200--175</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
@@ -18741,7 +18741,7 @@
       <c r="K357" s="2" t="inlineStr"/>
       <c r="L357" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18758,12 +18758,12 @@
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>20:-250--200</t>
+          <t>Ho:20:-250--200</t>
         </is>
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
@@ -18793,7 +18793,7 @@
       <c r="K358" s="2" t="inlineStr"/>
       <c r="L358" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18810,12 +18810,12 @@
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>20:-300--250</t>
+          <t>Ho:20:-300--250</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
@@ -18845,7 +18845,7 @@
       <c r="K359" s="2" t="inlineStr"/>
       <c r="L359" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18862,12 +18862,12 @@
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>21:10-20</t>
+          <t>Hu:21:10-20</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
@@ -18897,7 +18897,7 @@
       <c r="K360" s="2" t="inlineStr"/>
       <c r="L360" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18914,12 +18914,12 @@
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>21:0-10</t>
+          <t>Hu:21:0-10</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
@@ -18949,7 +18949,7 @@
       <c r="K361" s="2" t="inlineStr"/>
       <c r="L361" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18966,12 +18966,12 @@
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>21:-10-0</t>
+          <t>Ho:21:-10-0</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
@@ -19001,7 +19001,7 @@
       <c r="K362" s="2" t="inlineStr"/>
       <c r="L362" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19018,12 +19018,12 @@
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>21:-20--10</t>
+          <t>Ho:21:-20--10</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
@@ -19053,7 +19053,7 @@
       <c r="K363" s="2" t="inlineStr"/>
       <c r="L363" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19070,12 +19070,12 @@
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>21:-30--20</t>
+          <t>Ho:21:-30--20</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
@@ -19105,7 +19105,7 @@
       <c r="K364" s="2" t="inlineStr"/>
       <c r="L364" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19122,12 +19122,12 @@
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>21:-40--30</t>
+          <t>Ho:21:-40--30</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
@@ -19157,7 +19157,7 @@
       <c r="K365" s="2" t="inlineStr"/>
       <c r="L365" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19174,12 +19174,12 @@
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>21:-50--40</t>
+          <t>Ho:21:-50--40</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
@@ -19209,7 +19209,7 @@
       <c r="K366" s="2" t="inlineStr"/>
       <c r="L366" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19226,12 +19226,12 @@
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>21:-60--50</t>
+          <t>Ho:21:-60--50</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
@@ -19261,7 +19261,7 @@
       <c r="K367" s="2" t="inlineStr"/>
       <c r="L367" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19278,12 +19278,12 @@
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>21:-70--60</t>
+          <t>Ho:21:-70--60</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
@@ -19313,7 +19313,7 @@
       <c r="K368" s="2" t="inlineStr"/>
       <c r="L368" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19330,12 +19330,12 @@
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>21:-80--70</t>
+          <t>Ho:21:-80--70</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
@@ -19365,7 +19365,7 @@
       <c r="K369" s="2" t="inlineStr"/>
       <c r="L369" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19382,12 +19382,12 @@
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>21:-90--80</t>
+          <t>Ho:21:-90--80</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
@@ -19417,7 +19417,7 @@
       <c r="K370" s="2" t="inlineStr"/>
       <c r="L370" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19434,12 +19434,12 @@
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>21:-100--90</t>
+          <t>Ho:21:-100--90</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
@@ -19469,7 +19469,7 @@
       <c r="K371" s="2" t="inlineStr"/>
       <c r="L371" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19486,12 +19486,12 @@
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>21:-125--100</t>
+          <t>Ho:21:-125--100</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
@@ -19521,7 +19521,7 @@
       <c r="K372" s="2" t="inlineStr"/>
       <c r="L372" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19538,12 +19538,12 @@
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>21:-150--125</t>
+          <t>Ho:21:-150--125</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
@@ -19573,7 +19573,7 @@
       <c r="K373" s="2" t="inlineStr"/>
       <c r="L373" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19590,12 +19590,12 @@
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>21:-175--150</t>
+          <t>Ho:21:-175--150</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
@@ -19625,7 +19625,7 @@
       <c r="K374" s="2" t="inlineStr"/>
       <c r="L374" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19642,12 +19642,12 @@
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>21:-200--175</t>
+          <t>Ho:21:-200--175</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
@@ -19677,7 +19677,7 @@
       <c r="K375" s="2" t="inlineStr"/>
       <c r="L375" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19694,12 +19694,12 @@
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>21:-250--200</t>
+          <t>Ho:21:-250--200</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
@@ -19729,7 +19729,7 @@
       <c r="K376" s="2" t="inlineStr"/>
       <c r="L376" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column K (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
